--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Infrastructure Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Infrastructure Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="192">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Infrastructure Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -52,7 +52,7 @@
     <t>Yield to Call @</t>
   </si>
   <si>
-    <t>Equity &amp; Equity Related Instruments</t>
+    <t>Equity &amp; Equity Related Instruments (Note -1)</t>
   </si>
   <si>
     <t/>
@@ -70,6 +70,72 @@
     <t>Construction</t>
   </si>
   <si>
+    <t>Adani Ports and Special Economic Zone Ltd.</t>
+  </si>
+  <si>
+    <t>INE742F01042</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
+    <t>NCC Ltd.</t>
+  </si>
+  <si>
+    <t>INE868B01028</t>
+  </si>
+  <si>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Reliance Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE002A01018</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
+  </si>
+  <si>
+    <t>Jm Financial Ltd.</t>
+  </si>
+  <si>
+    <t>INE780C01023</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Kalpataru Projects International Ltd</t>
+  </si>
+  <si>
+    <t>INE220B01022</t>
+  </si>
+  <si>
+    <t>ICICI Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE090A01021</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
     <t>Shree Cements Ltd.</t>
   </si>
   <si>
@@ -79,46 +145,97 @@
     <t>Cement &amp; Cement Products</t>
   </si>
   <si>
-    <t>Adani Ports and Special Economic Zone Ltd.</t>
-  </si>
-  <si>
-    <t>INE742F01042</t>
-  </si>
-  <si>
-    <t>Transport Infrastructure</t>
-  </si>
-  <si>
-    <t>NCC Ltd.</t>
-  </si>
-  <si>
-    <t>INE868B01028</t>
-  </si>
-  <si>
-    <t>ICICI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE090A01021</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>NTPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE733E01010</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
+    <t>CESC Ltd.</t>
+  </si>
+  <si>
+    <t>INE486A01021</t>
+  </si>
+  <si>
+    <t>AIA Engineering Ltd.</t>
+  </si>
+  <si>
+    <t>INE212H01026</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>Nuvoco Vistas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE118D01016</t>
+  </si>
+  <si>
+    <t>Gujarat Gas Ltd.</t>
+  </si>
+  <si>
+    <t>INE844O01030</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Oberoi Realty Ltd.</t>
+  </si>
+  <si>
+    <t>INE093I01010</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>KSB Ltd.</t>
+  </si>
+  <si>
+    <t>INE999A01023</t>
+  </si>
+  <si>
+    <t>Ratnamani Metals &amp; Tubes Ltd.</t>
+  </si>
+  <si>
+    <t>INE703B01027</t>
+  </si>
+  <si>
+    <t>Ambuja Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE079A01024</t>
+  </si>
+  <si>
+    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE213A01029</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>IndusInd Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE095A01012</t>
   </si>
   <si>
     <t>HDFC Bank Ltd.</t>
@@ -127,67 +244,43 @@
     <t>INE040A01034</t>
   </si>
   <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>Reliance Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE002A01018</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>Jm Financial Ltd.</t>
-  </si>
-  <si>
-    <t>INE780C01023</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Kalpataru Projects International Ltd</t>
-  </si>
-  <si>
-    <t>INE220B01022</t>
-  </si>
-  <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>Nuvoco Vistas Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE118D01016</t>
-  </si>
-  <si>
-    <t>Oil &amp; Natural Gas Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE213A01029</t>
-  </si>
-  <si>
-    <t>Oil</t>
-  </si>
-  <si>
-    <t>AIA Engineering Ltd.</t>
-  </si>
-  <si>
-    <t>INE212H01026</t>
+    <t>Ingersoll - Rand (India) Ltd</t>
+  </si>
+  <si>
+    <t>INE177A01018</t>
+  </si>
+  <si>
+    <t>INOX India Ltd</t>
+  </si>
+  <si>
+    <t>INE616N01034</t>
+  </si>
+  <si>
+    <t>SBI Cards &amp; Payment Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE018E01016</t>
+  </si>
+  <si>
+    <t>State Bank Of India</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
+  </si>
+  <si>
+    <t>IRB Infrastructure Developers Ltd.</t>
+  </si>
+  <si>
+    <t>INE821I01022</t>
+  </si>
+  <si>
+    <t>Hindalco Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE038A01020</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
   </si>
   <si>
     <t>Bajaj Finserv Ltd.</t>
@@ -196,49 +289,13 @@
     <t>INE918I01026</t>
   </si>
   <si>
-    <t>Ratnamani Metals &amp; Tubes Ltd.</t>
-  </si>
-  <si>
-    <t>INE703B01027</t>
-  </si>
-  <si>
-    <t>Gujarat Gas Ltd.</t>
-  </si>
-  <si>
-    <t>INE844O01030</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>CESC Ltd.</t>
-  </si>
-  <si>
-    <t>INE486A01021</t>
-  </si>
-  <si>
-    <t>State Bank Of India</t>
-  </si>
-  <si>
-    <t>INE062A01020</t>
-  </si>
-  <si>
-    <t>Ingersoll - Rand (India) Ltd</t>
-  </si>
-  <si>
-    <t>INE177A01018</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
   </si>
   <si>
     <t>Delhivery Ltd.</t>
@@ -247,25 +304,25 @@
     <t>INE148O01028</t>
   </si>
   <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>SBI Cards &amp; Payment Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE018E01016</t>
-  </si>
-  <si>
-    <t>Hindalco Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE038A01020</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
+    <t>SKF India Ltd.</t>
+  </si>
+  <si>
+    <t>INE640A01023</t>
+  </si>
+  <si>
+    <t>ACC Ltd.</t>
+  </si>
+  <si>
+    <t>INE012A01025</t>
+  </si>
+  <si>
+    <t>CIE Automotive India Ltd</t>
+  </si>
+  <si>
+    <t>INE536H01010</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
   </si>
   <si>
     <t>Tata Steel Ltd.</t>
@@ -277,70 +334,94 @@
     <t>Ferrous Metals</t>
   </si>
   <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>KSB Ltd.</t>
-  </si>
-  <si>
-    <t>INE999A01023</t>
-  </si>
-  <si>
-    <t>ACC Ltd.</t>
-  </si>
-  <si>
-    <t>INE012A01025</t>
-  </si>
-  <si>
-    <t>INOX India Ltd</t>
-  </si>
-  <si>
-    <t>INE616N01034</t>
-  </si>
-  <si>
-    <t>CIE Automotive India Ltd</t>
-  </si>
-  <si>
-    <t>INE536H01010</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
     <t>Hindustan Petroleum Corporation Ltd.</t>
   </si>
   <si>
     <t>INE094A01015</t>
   </si>
   <si>
-    <t>IRB Infrastructure Developers Ltd.</t>
-  </si>
-  <si>
-    <t>INE821I01022</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE095A01012</t>
-  </si>
-  <si>
     <t>PSP Projects Ltd</t>
   </si>
   <si>
     <t>INE488V01015</t>
   </si>
   <si>
-    <t>JSW Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE019A01038</t>
+    <t>Prestige Estates Projects Ltd.</t>
+  </si>
+  <si>
+    <t>INE811K01011</t>
+  </si>
+  <si>
+    <t>Grindwell Norton Ltd.</t>
+  </si>
+  <si>
+    <t>INE536A01023</t>
+  </si>
+  <si>
+    <t>Coal India Ltd.</t>
+  </si>
+  <si>
+    <t>INE522F01014</t>
+  </si>
+  <si>
+    <t>Consumable Fuels</t>
+  </si>
+  <si>
+    <t>RR Kabel Ltd.</t>
+  </si>
+  <si>
+    <t>INE777K01022</t>
+  </si>
+  <si>
+    <t>Orient Refractories Ltd.</t>
+  </si>
+  <si>
+    <t>INE743M01012</t>
+  </si>
+  <si>
+    <t>Chemplast Sanmar Ltd</t>
+  </si>
+  <si>
+    <t>INE488A01050</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
+    <t>Rain Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE855B01025</t>
+  </si>
+  <si>
+    <t>Container Corporation Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE111A01025</t>
+  </si>
+  <si>
+    <t>BEML Ltd.</t>
+  </si>
+  <si>
+    <t>INE258A01016</t>
+  </si>
+  <si>
+    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+  </si>
+  <si>
+    <t>Route Mobile Ltd.</t>
+  </si>
+  <si>
+    <t>INE450U01017</t>
+  </si>
+  <si>
+    <t>GMM Pfaudler Ltd.</t>
+  </si>
+  <si>
+    <t>INE541A01023</t>
+  </si>
+  <si>
+    <t>Industrial Manufacturing</t>
   </si>
   <si>
     <t>Power Grid Corporation Of India Ltd.</t>
@@ -349,76 +430,10 @@
     <t>INE752E01010</t>
   </si>
   <si>
-    <t>Chemplast Sanmar Ltd</t>
-  </si>
-  <si>
-    <t>INE488A01050</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>Dalmia Bharat Ltd.</t>
-  </si>
-  <si>
-    <t>INE00R701025</t>
-  </si>
-  <si>
-    <t>NTPC Green Energy Ltd</t>
-  </si>
-  <si>
-    <t>INE0ONG01011</t>
-  </si>
-  <si>
-    <t>Container Corporation Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE111A01025</t>
-  </si>
-  <si>
-    <t>RR Kabel Ltd.</t>
-  </si>
-  <si>
-    <t>INE777K01022</t>
-  </si>
-  <si>
-    <t>Jindal Stainless Ltd.</t>
-  </si>
-  <si>
-    <t>INE220G01021</t>
-  </si>
-  <si>
-    <t>GMM Pfaudler Ltd.</t>
-  </si>
-  <si>
-    <t>INE541A01023</t>
-  </si>
-  <si>
-    <t>Industrial Manufacturing</t>
-  </si>
-  <si>
-    <t>BEML Ltd.</t>
-  </si>
-  <si>
-    <t>INE258A01016</t>
-  </si>
-  <si>
-    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
-  </si>
-  <si>
-    <t>Oberoi Realty Ltd.</t>
-  </si>
-  <si>
-    <t>INE093I01010</t>
-  </si>
-  <si>
-    <t>Realty</t>
+    <t>NHPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE848E01016</t>
   </si>
   <si>
     <t>Heidleberg Cement India Ltd.</t>
@@ -433,81 +448,36 @@
     <t>INE279A01012</t>
   </si>
   <si>
+    <t>Birla Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE340A01012</t>
+  </si>
+  <si>
+    <t>Afcons Infrastructure Ltd.</t>
+  </si>
+  <si>
+    <t>INE101I01011</t>
+  </si>
+  <si>
     <t>Gateway Distriparks Ltd.</t>
   </si>
   <si>
     <t>INE079J01017</t>
   </si>
   <si>
+    <t>Sagar Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE229C01021</t>
+  </si>
+  <si>
     <t>Gujarat Pipavav Port Ltd.</t>
   </si>
   <si>
     <t>INE517F01014</t>
   </si>
   <si>
-    <t>NHPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE848E01016</t>
-  </si>
-  <si>
-    <t>Afcons Infrastructure Ltd.</t>
-  </si>
-  <si>
-    <t>INE101I01011</t>
-  </si>
-  <si>
-    <t>Birla Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE340A01012</t>
-  </si>
-  <si>
-    <t>Sagar Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE229C01021</t>
-  </si>
-  <si>
-    <t>Gujarat State Petronet Ltd.</t>
-  </si>
-  <si>
-    <t>INE246F01010</t>
-  </si>
-  <si>
-    <t>Siemens Ltd.</t>
-  </si>
-  <si>
-    <t>INE003A01024</t>
-  </si>
-  <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>Jindal Steel &amp; Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE749A01030</t>
-  </si>
-  <si>
-    <t>Rain Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE855B01025</t>
-  </si>
-  <si>
-    <t>Route Mobile Ltd.</t>
-  </si>
-  <si>
-    <t>INE450U01017</t>
-  </si>
-  <si>
-    <t>Grindwell Norton Ltd.</t>
-  </si>
-  <si>
-    <t>INE536A01023</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -544,31 +514,19 @@
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X409</t>
+    <t>IN002024X516</t>
   </si>
   <si>
     <t>SOV</t>
   </si>
   <si>
-    <t>364 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002023Z471</t>
-  </si>
-  <si>
     <t>182 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024Y191</t>
-  </si>
-  <si>
-    <t>IN002023Z513</t>
-  </si>
-  <si>
-    <t>IN002024Y225</t>
-  </si>
-  <si>
-    <t>IN002024X383</t>
+    <t>IN002024Y407</t>
+  </si>
+  <si>
+    <t>IN002025X034</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -598,16 +556,31 @@
     <t>Total Net Assets</t>
   </si>
   <si>
+    <t>Details of Stock Future / Index Future</t>
+  </si>
+  <si>
+    <t>Stock / Index Futures</t>
+  </si>
+  <si>
+    <t>NCC Ltd. $$</t>
+  </si>
+  <si>
+    <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
+    <t>$$ - Derivatives.</t>
+  </si>
+  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -617,9 +590,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - BSE India Infrastructure TRI</t>
   </si>
 </sst>
 </file>
@@ -990,13 +960,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>134</xdr:row>
+      <xdr:row>137</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1014,8 +984,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="24079200"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:off x="666750" y="24650700"/>
+          <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1029,13 +999,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>149</xdr:row>
+      <xdr:row>152</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1053,8 +1023,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="26936700"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:off x="666750" y="27508200"/>
+          <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1387,12 +1357,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J138"/>
+  <dimension ref="B1:J140"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.857142857142858" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.857142857142854" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.571428571428573" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="50.285714285714285" collapsed="true"/>
     <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.0" collapsed="true"/>
@@ -1487,10 +1457,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>693649.8700000001</v>
+        <v>736115.40</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9329608249343998</v>
+        <v>0.9294049052534</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1524,10 +1494,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>693649.8700000001</v>
+        <v>736115.40</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9329608249343998</v>
+        <v>0.9294049052534</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1550,13 +1520,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>1925850</v>
+        <v>2130204</v>
       </c>
       <c r="G8" s="15">
-        <v>68702.77</v>
+        <v>78287.13</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0924053989582</v>
+        <v>0.0988437990027</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1579,13 +1549,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>108747</v>
+        <v>2468659</v>
       </c>
       <c r="G9" s="15">
-        <v>30227.21</v>
+        <v>35370.95</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0406556737005</v>
+        <v>0.0446586695966</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1605,16 +1575,16 @@
         <v>13</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F10" s="14">
-        <v>2695324</v>
+        <v>12522005</v>
       </c>
       <c r="G10" s="15">
-        <v>29631.04</v>
+        <v>28949.62</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0398538235466</v>
+        <v>0.036551223943</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1625,25 +1595,25 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1">
       <c r="B11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F11" s="14">
-        <v>10506117</v>
+        <v>7600000</v>
       </c>
       <c r="G11" s="15">
-        <v>26506.93</v>
+        <v>25376.40</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0356518877158</v>
+        <v>0.0320397462649</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1666,13 +1636,13 @@
         <v>28</v>
       </c>
       <c r="F12" s="14">
-        <v>1990000</v>
+        <v>1662727</v>
       </c>
       <c r="G12" s="15">
-        <v>24930.72</v>
+        <v>23625.69</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0335318812897</v>
+        <v>0.0298293340637</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1695,13 +1665,13 @@
         <v>31</v>
       </c>
       <c r="F13" s="14">
-        <v>7260775</v>
+        <v>5223662</v>
       </c>
       <c r="G13" s="15">
-        <v>23524.91</v>
+        <v>22751.66</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0316410632934</v>
+        <v>0.0287258008822</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1724,13 +1694,13 @@
         <v>34</v>
       </c>
       <c r="F14" s="14">
-        <v>4823662</v>
+        <v>17763241</v>
       </c>
       <c r="G14" s="15">
-        <v>21291.64</v>
+        <v>22690.76</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0286373095098</v>
+        <v>0.0286489097334</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1750,16 +1720,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F15" s="14">
-        <v>1225000</v>
+        <v>1903566</v>
       </c>
       <c r="G15" s="15">
-        <v>20809.69</v>
+        <v>21676.86</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0279890855441</v>
+        <v>0.0273687794258</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1782,13 +1752,13 @@
         <v>39</v>
       </c>
       <c r="F16" s="14">
-        <v>477106</v>
+        <v>1425000</v>
       </c>
       <c r="G16" s="15">
-        <v>20631.73</v>
+        <v>20602.65</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0277497288951</v>
+        <v>0.0260125028919</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1811,13 +1781,13 @@
         <v>42</v>
       </c>
       <c r="F17" s="14">
-        <v>1609486</v>
+        <v>66000</v>
       </c>
       <c r="G17" s="15">
-        <v>20361.61</v>
+        <v>19532.70</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0273864168137</v>
+        <v>0.0246616049506</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1837,16 +1807,16 @@
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
-        <v>17763241</v>
+        <v>12000502</v>
       </c>
       <c r="G18" s="15">
-        <v>19552</v>
+        <v>19488.82</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0262974893214</v>
+        <v>0.0246062029209</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1857,25 +1827,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F19" s="14">
-        <v>1753566</v>
+        <v>540770</v>
       </c>
       <c r="G19" s="15">
-        <v>18564.13</v>
+        <v>18915.59</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0249688016795</v>
+        <v>0.0238824539356</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1895,16 +1865,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F20" s="14">
-        <v>635000</v>
+        <v>550000</v>
       </c>
       <c r="G20" s="15">
-        <v>18504.22</v>
+        <v>17974.55</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0248882225783</v>
+        <v>0.0226943152388</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1915,25 +1885,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>52</v>
-      </c>
       <c r="D21" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F21" s="14">
-        <v>4957792</v>
+        <v>1496057</v>
       </c>
       <c r="G21" s="15">
-        <v>17377.06</v>
+        <v>17835.99</v>
       </c>
       <c r="H21" s="16">
-        <v>0.023372189535</v>
+        <v>0.0225193720931</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1944,25 +1914,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="D22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F22" s="14">
-        <v>6535086</v>
+        <v>4957792</v>
       </c>
       <c r="G22" s="15">
-        <v>17161.79</v>
+        <v>17741.46</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0230826508419</v>
+        <v>0.0224000203642</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1973,25 +1943,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="F23" s="14">
-        <v>450770</v>
+        <v>3519895</v>
       </c>
       <c r="G23" s="15">
-        <v>16591.04</v>
+        <v>16193.28</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0223149906522</v>
+        <v>0.0204453185793</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2002,25 +1972,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="D24" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>45</v>
-      </c>
       <c r="F24" s="14">
-        <v>874529</v>
+        <v>917809</v>
       </c>
       <c r="G24" s="15">
-        <v>15182.70</v>
+        <v>16027.70</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0204207697995</v>
+        <v>0.0202362605102</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2040,16 +2010,16 @@
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F25" s="14">
-        <v>493497</v>
+        <v>290457</v>
       </c>
       <c r="G25" s="15">
-        <v>14107.11</v>
+        <v>15481.36</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0189740985363</v>
+        <v>0.0195464623128</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2060,25 +2030,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="F26" s="14">
-        <v>2803340</v>
+        <v>1805754</v>
       </c>
       <c r="G26" s="15">
-        <v>13624.23</v>
+        <v>15280.29</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0183246237182</v>
+        <v>0.0192925952639</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2098,16 +2068,16 @@
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F27" s="14">
-        <v>9324866</v>
+        <v>529197</v>
       </c>
       <c r="G27" s="15">
-        <v>13332.69</v>
+        <v>15023.90</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0179325016827</v>
+        <v>0.018968882265</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2127,16 +2097,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F28" s="14">
-        <v>1715608</v>
+        <v>2672608</v>
       </c>
       <c r="G28" s="15">
-        <v>13259.93</v>
+        <v>14792.89</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0178346392992</v>
+        <v>0.0186772135577</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2156,16 +2126,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F29" s="14">
-        <v>347555</v>
+        <v>6172586</v>
       </c>
       <c r="G29" s="15">
-        <v>13006.03</v>
+        <v>14777.17</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0174931431587</v>
+        <v>0.0186573657931</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2176,25 +2146,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F30" s="14">
-        <v>1096057</v>
+        <v>1774016</v>
       </c>
       <c r="G30" s="15">
-        <v>10808.22</v>
+        <v>14492.82</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0145370831646</v>
+        <v>0.0182983510452</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2205,25 +2175,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F31" s="14">
-        <v>430000</v>
+        <v>691000</v>
       </c>
       <c r="G31" s="15">
-        <v>10788.06</v>
+        <v>13439.26</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0145099679137</v>
+        <v>0.0169681467973</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2234,25 +2204,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F32" s="14">
-        <v>3315972</v>
+        <v>340670</v>
       </c>
       <c r="G32" s="15">
-        <v>10645.93</v>
+        <v>13350.18</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0143188027052</v>
+        <v>0.0168556761318</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2263,25 +2233,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F33" s="14">
-        <v>2072608</v>
+        <v>1054466</v>
       </c>
       <c r="G33" s="15">
-        <v>10628.33</v>
+        <v>12589.80</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0142951306608</v>
+        <v>0.0158956352172</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2292,25 +2262,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F34" s="14">
-        <v>1343343</v>
+        <v>1364189</v>
       </c>
       <c r="G34" s="15">
-        <v>10453.90</v>
+        <v>12564.86</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0140605218707</v>
+        <v>0.015864146461</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2321,25 +2291,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="F35" s="14">
-        <v>1554000</v>
+        <v>1490608</v>
       </c>
       <c r="G35" s="15">
-        <v>9235.42</v>
+        <v>12108.21</v>
       </c>
       <c r="H35" s="16">
-        <v>0.012421663197</v>
+        <v>0.0152875891033</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2359,16 +2329,16 @@
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="F36" s="14">
-        <v>6700000</v>
+        <v>19885692</v>
       </c>
       <c r="G36" s="15">
-        <v>9019.54</v>
+        <v>10195.39</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0121313040525</v>
+        <v>0.012872499987</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2379,25 +2349,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="D37" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D37" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>89</v>
-      </c>
       <c r="F37" s="14">
-        <v>546371</v>
+        <v>1600162</v>
       </c>
       <c r="G37" s="15">
-        <v>8885.63</v>
+        <v>10137.03</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0119511947647</v>
+        <v>0.0127988157926</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2408,25 +2378,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>91</v>
-      </c>
       <c r="D38" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="F38" s="14">
-        <v>1201514</v>
+        <v>474529</v>
       </c>
       <c r="G38" s="15">
-        <v>8441.24</v>
+        <v>9573.15</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0113534890937</v>
+        <v>0.0120868719344</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2437,25 +2407,25 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="D39" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D39" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="F39" s="14">
-        <v>419776</v>
+        <v>480373</v>
       </c>
       <c r="G39" s="15">
-        <v>8427.63</v>
+        <v>8916.68</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0113351836093</v>
+        <v>0.0112580257532</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2475,16 +2445,16 @@
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F40" s="14">
-        <v>829913</v>
+        <v>2477632</v>
       </c>
       <c r="G40" s="15">
-        <v>7606.15</v>
+        <v>8869.92</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0102302909371</v>
+        <v>0.0111989874919</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2504,16 +2474,16 @@
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="F41" s="14">
-        <v>1622376</v>
+        <v>171994</v>
       </c>
       <c r="G41" s="15">
-        <v>7535.13</v>
+        <v>8076.84</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0101347688579</v>
+        <v>0.0101976601969</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2524,10 +2494,10 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>99</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>100</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>13</v>
@@ -2536,13 +2506,13 @@
         <v>42</v>
       </c>
       <c r="F42" s="14">
-        <v>2100000</v>
+        <v>419776</v>
       </c>
       <c r="G42" s="15">
-        <v>7523.25</v>
+        <v>7903.54</v>
       </c>
       <c r="H42" s="16">
-        <v>0.010118790228</v>
+        <v>0.0099788550068</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2553,25 +2523,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="D43" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D43" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F43" s="14">
-        <v>12375315</v>
+        <v>1622376</v>
       </c>
       <c r="G43" s="15">
-        <v>7093.53</v>
+        <v>7296.64</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0095408157439</v>
+        <v>0.009212594938</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2591,16 +2561,16 @@
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="F44" s="14">
-        <v>700000</v>
+        <v>4265182</v>
       </c>
       <c r="G44" s="15">
-        <v>6938.40</v>
+        <v>6867.80</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0093321655026</v>
+        <v>0.0086711499424</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2611,25 +2581,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F45" s="14">
-        <v>1018942</v>
+        <v>1591103</v>
       </c>
       <c r="G45" s="15">
-        <v>6455</v>
+        <v>6540.23</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0086819912832</v>
+        <v>0.0082575664678</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2640,25 +2610,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="F46" s="14">
-        <v>676005</v>
+        <v>1018942</v>
       </c>
       <c r="G46" s="15">
-        <v>6388.25</v>
+        <v>6511.55</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0085922123648</v>
+        <v>0.0082213556608</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2669,25 +2639,25 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="F47" s="14">
-        <v>1999537</v>
+        <v>410509</v>
       </c>
       <c r="G47" s="15">
-        <v>6031.60</v>
+        <v>6020.52</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0081125172151</v>
+        <v>0.0076013907876</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2698,25 +2668,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="F48" s="14">
-        <v>1020472</v>
+        <v>280082</v>
       </c>
       <c r="G48" s="15">
-        <v>4843.16</v>
+        <v>5031.95</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0065140624172</v>
+        <v>0.0063532416425</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2736,16 +2706,16 @@
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="F49" s="14">
-        <v>1834598</v>
+        <v>1155000</v>
       </c>
       <c r="G49" s="15">
-        <v>4790.14</v>
+        <v>4588.82</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0064427503835</v>
+        <v>0.0057937543723</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2756,25 +2726,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F50" s="14">
-        <v>234321</v>
+        <v>319086</v>
       </c>
       <c r="G50" s="15">
-        <v>4373.25</v>
+        <v>4549.21</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0058820322818</v>
+        <v>0.0057437435611</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2785,25 +2755,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F51" s="14">
-        <v>3645450</v>
+        <v>985277</v>
       </c>
       <c r="G51" s="15">
-        <v>4188.99</v>
+        <v>4542.13</v>
       </c>
       <c r="H51" s="16">
-        <v>0.005634202117</v>
+        <v>0.0057348044916</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2814,25 +2784,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D52" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="F52" s="14">
-        <v>521196</v>
+        <v>990391</v>
       </c>
       <c r="G52" s="15">
-        <v>4065.85</v>
+        <v>4203.71</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0054685785064</v>
+        <v>0.0053075220193</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2843,25 +2813,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C53" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D53" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="F53" s="14">
-        <v>319086</v>
+        <v>2970918</v>
       </c>
       <c r="G53" s="15">
-        <v>3911.99</v>
+        <v>4191.97</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0052616364183</v>
+        <v>0.0052926993249</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -2872,25 +2842,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="F54" s="14">
-        <v>573420</v>
+        <v>521196</v>
       </c>
       <c r="G54" s="15">
-        <v>3746.15</v>
+        <v>4088.26</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0050385811999</v>
+        <v>0.0051617571075</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -2901,25 +2871,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F55" s="14">
-        <v>302551</v>
+        <v>88835</v>
       </c>
       <c r="G55" s="15">
-        <v>3599.60</v>
+        <v>3757.81</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0048414710802</v>
+        <v>0.0047445374013</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -2930,25 +2900,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="F56" s="14">
-        <v>88835</v>
+        <v>389457</v>
       </c>
       <c r="G56" s="15">
-        <v>3415.44</v>
+        <v>3696.92</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0045937754157</v>
+        <v>0.0046676588784</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -2959,25 +2929,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F57" s="14">
-        <v>160314</v>
+        <v>302551</v>
       </c>
       <c r="G57" s="15">
-        <v>2905.93</v>
+        <v>3426.09</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0039084831804</v>
+        <v>0.0043257142179</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -2988,25 +2958,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D58" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F58" s="14">
-        <v>1286961</v>
+        <v>1099537</v>
       </c>
       <c r="G58" s="15">
-        <v>2806.60</v>
+        <v>3185.91</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0037748840798</v>
+        <v>0.004022467648</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3017,25 +2987,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F59" s="14">
-        <v>403309</v>
+        <v>3000000</v>
       </c>
       <c r="G59" s="15">
-        <v>2571.7</v>
+        <v>2622.30</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0034589429873</v>
+        <v>0.0033108646865</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3046,25 +3016,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F60" s="14">
-        <v>3327884</v>
+        <v>1286961</v>
       </c>
       <c r="G60" s="15">
-        <v>2533.52</v>
+        <v>2541.62</v>
       </c>
       <c r="H60" s="16">
-        <v>0.003407590791</v>
+        <v>0.0032089996966</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3075,25 +3045,25 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D61" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="F61" s="14">
-        <v>1656439</v>
+        <v>403309</v>
       </c>
       <c r="G61" s="15">
-        <v>2513.81</v>
+        <v>2408.36</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0033810807912</v>
+        <v>0.0030407482272</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3104,25 +3074,25 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F62" s="14">
-        <v>3000000</v>
+        <v>166453</v>
       </c>
       <c r="G62" s="15">
-        <v>2416.50</v>
+        <v>2287.73</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0032501985958</v>
+        <v>0.0028884431488</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3133,10 +3103,10 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
@@ -3148,10 +3118,10 @@
         <v>507823</v>
       </c>
       <c r="G63" s="15">
-        <v>2398.96</v>
+        <v>2148.35</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0032266072515</v>
+        <v>0.0027124646872</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3162,25 +3132,25 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F64" s="14">
-        <v>200000</v>
+        <v>3327884</v>
       </c>
       <c r="G64" s="15">
-        <v>2335</v>
+        <v>2120.86</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0031405808902</v>
+        <v>0.0026777563509</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3191,25 +3161,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F65" s="14">
-        <v>745273</v>
+        <v>834421</v>
       </c>
       <c r="G65" s="15">
-        <v>1541.37</v>
+        <v>2003.53</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0020731465382</v>
+        <v>0.0025296177879</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3220,25 +3190,25 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="F66" s="14">
-        <v>381846</v>
+        <v>555898</v>
       </c>
       <c r="G66" s="15">
-        <v>1320.04</v>
+        <v>868.03</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0017754571299</v>
+        <v>0.0010959576989</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3249,56 +3219,35 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="C67" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" ht="15" customHeight="1">
+      <c r="B68" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="D67" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="13" t="s">
+      <c r="C68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="F67" s="14">
-        <v>20000</v>
-      </c>
-      <c r="G67" s="15">
-        <v>1214.67</v>
-      </c>
-      <c r="H67" s="16">
-        <v>0.0016337342141</v>
-      </c>
-      <c r="I67" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" ht="15" customHeight="1">
-      <c r="B68" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F68" s="14">
-        <v>99931</v>
-      </c>
-      <c r="G68" s="15">
-        <v>791</v>
-      </c>
-      <c r="H68" s="16">
-        <v>0.0010638969953</v>
-      </c>
-      <c r="I68" s="15" t="s">
+      <c r="H68" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I68" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J68" s="11" t="s">
@@ -3307,27 +3256,6 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C69" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D69" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="F69" s="14">
-        <v>406049</v>
-      </c>
-      <c r="G69" s="15">
-        <v>588.41</v>
-      </c>
-      <c r="H69" s="16">
-        <v>0.0007914129343</v>
-      </c>
-      <c r="I69" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J69" s="11" t="s">
@@ -3335,28 +3263,28 @@
       </c>
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
-      <c r="B70" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="C70" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="F70" s="14">
-        <v>48582</v>
-      </c>
-      <c r="G70" s="15">
-        <v>581.53</v>
-      </c>
-      <c r="H70" s="16">
-        <v>0.0007821593169</v>
-      </c>
-      <c r="I70" s="15" t="s">
+      <c r="B70" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I70" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J70" s="11" t="s">
@@ -3365,361 +3293,361 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" ht="15" customHeight="1">
+      <c r="B72" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" ht="15" customHeight="1">
+      <c r="B73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" ht="15" customHeight="1">
+      <c r="B74" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="15" customHeight="1">
+      <c r="B75" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="15" customHeight="1">
+      <c r="B76" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" ht="15" customHeight="1">
+      <c r="B77" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="15" customHeight="1">
+      <c r="B78" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" ht="15" customHeight="1">
+      <c r="B79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="15" customHeight="1">
+      <c r="B80" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15" customHeight="1">
+      <c r="B81" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" ht="15" customHeight="1">
+      <c r="B82" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="9">
+        <v>4873.110000000001</v>
+      </c>
+      <c r="H82" s="10">
+        <v>0.006152693365499999</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" ht="15" customHeight="1">
+      <c r="B83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="15" customHeight="1">
+      <c r="B84" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" ht="15" customHeight="1">
+      <c r="B85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="15" customHeight="1">
+      <c r="B86" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="D71" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F71" s="14">
-        <v>21265</v>
-      </c>
-      <c r="G71" s="15">
-        <v>409.87</v>
-      </c>
-      <c r="H71" s="16">
-        <v>0.0005512761839</v>
-      </c>
-      <c r="I71" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" ht="15" customHeight="1">
-      <c r="B72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J72" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" ht="15" customHeight="1">
-      <c r="B73" s="7" t="s">
+      <c r="C86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="15" customHeight="1">
+      <c r="B87" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" ht="15" customHeight="1">
+      <c r="B88" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" s="9" t="s">
+      <c r="C88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="9">
+        <v>4873.110000000001</v>
+      </c>
+      <c r="H88" s="10">
+        <v>0.006152693365499999</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J88" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" ht="15" customHeight="1">
+      <c r="B89" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="H73" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="I73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J73" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" ht="15" customHeight="1">
-      <c r="B74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" ht="15" customHeight="1">
-      <c r="B75" s="7" t="s">
+      <c r="C89" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="C75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="I75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J75" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" ht="15" customHeight="1">
-      <c r="B76" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J76" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" ht="15" customHeight="1">
-      <c r="B77" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="I77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J77" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" ht="15" customHeight="1">
-      <c r="B78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" ht="15" customHeight="1">
-      <c r="B79" s="7" t="s">
+      <c r="D89" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="I79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J79" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" ht="15" customHeight="1">
-      <c r="B80" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="I81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" ht="15" customHeight="1">
-      <c r="B82" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J82" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="I83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="I85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" customHeight="1">
-      <c r="B86" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J86" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" ht="15" customHeight="1">
-      <c r="B87" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" s="9">
-        <v>7233.27</v>
-      </c>
-      <c r="H87" s="10">
-        <v>0.009728766396099998</v>
-      </c>
-      <c r="I87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" ht="15" customHeight="1">
-      <c r="B88" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J88" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" ht="15" customHeight="1">
-      <c r="B89" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="I89" s="9" t="s">
-        <v>13</v>
+      <c r="F89" s="14">
+        <v>2400000</v>
+      </c>
+      <c r="G89" s="15">
+        <v>2390.67</v>
+      </c>
+      <c r="H89" s="16">
+        <v>0.0030184131793</v>
+      </c>
+      <c r="I89" s="15">
+        <v>5.70</v>
       </c>
       <c r="J89" s="11" t="s">
         <v>13</v>
@@ -3727,36 +3655,57 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
-        <v>13</v>
+        <v>168</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="F90" s="14">
+        <v>2200000</v>
+      </c>
+      <c r="G90" s="15">
+        <v>2184.55</v>
+      </c>
+      <c r="H90" s="16">
+        <v>0.0027581700991</v>
+      </c>
+      <c r="I90" s="15">
+        <v>5.61</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="9" t="s">
+      <c r="B91" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="H91" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="I91" s="9" t="s">
-        <v>13</v>
+      <c r="C91" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="F91" s="14">
+        <v>300000</v>
+      </c>
+      <c r="G91" s="15">
+        <v>297.89</v>
+      </c>
+      <c r="H91" s="16">
+        <v>0.0003761100871</v>
+      </c>
+      <c r="I91" s="15">
+        <v>5.61</v>
       </c>
       <c r="J91" s="11" t="s">
         <v>13</v>
@@ -3772,7 +3721,7 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
       <c r="B93" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>13</v>
@@ -3787,10 +3736,10 @@
         <v>13</v>
       </c>
       <c r="G93" s="9">
-        <v>7233.27</v>
+        <v>4500.52</v>
       </c>
       <c r="H93" s="10">
-        <v>0.009728766396099998</v>
+        <v>0.0056822685195</v>
       </c>
       <c r="I93" s="9" t="s">
         <v>13</v>
@@ -3801,28 +3750,28 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D94" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F94" s="14">
-        <v>5000000</v>
+        <v>1179999</v>
       </c>
       <c r="G94" s="15">
-        <v>4939.98</v>
+        <v>4500.52</v>
       </c>
       <c r="H94" s="16">
-        <v>0.0066442855614</v>
-      </c>
-      <c r="I94" s="15">
-        <v>6.52</v>
+        <v>0.0056822685195</v>
+      </c>
+      <c r="I94" s="15" t="s">
+        <v>13</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>13</v>
@@ -3830,57 +3779,36 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C95" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="F95" s="14">
-        <v>800000</v>
-      </c>
-      <c r="G95" s="15">
-        <v>799.30</v>
-      </c>
-      <c r="H95" s="16">
-        <v>0.0010750605162</v>
-      </c>
-      <c r="I95" s="15">
-        <v>6.37</v>
+        <v>13</v>
       </c>
       <c r="J95" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
-      <c r="B96" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="C96" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="D96" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="F96" s="14">
-        <v>500000</v>
-      </c>
-      <c r="G96" s="15">
-        <v>499.56</v>
-      </c>
-      <c r="H96" s="16">
-        <v>0.0006719094601</v>
-      </c>
-      <c r="I96" s="15">
-        <v>6.37</v>
+      <c r="B96" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H96" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J96" s="11" t="s">
         <v>13</v>
@@ -3888,57 +3816,36 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
       <c r="B97" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C97" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="D97" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="F97" s="14">
-        <v>500000</v>
-      </c>
-      <c r="G97" s="15">
-        <v>497.72</v>
-      </c>
-      <c r="H97" s="16">
-        <v>0.0006694346555</v>
-      </c>
-      <c r="I97" s="15">
-        <v>6.43</v>
+        <v>13</v>
       </c>
       <c r="J97" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
-      <c r="B98" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="C98" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D98" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E98" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="F98" s="14">
-        <v>300000</v>
-      </c>
-      <c r="G98" s="15">
-        <v>298.63</v>
-      </c>
-      <c r="H98" s="16">
-        <v>0.0004016581033</v>
-      </c>
-      <c r="I98" s="15">
-        <v>6.43</v>
+      <c r="B98" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="9">
+        <v>47952.73</v>
+      </c>
+      <c r="H98" s="10">
+        <v>0.0605441789187</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>13</v>
@@ -3946,64 +3853,57 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="C99" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D99" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J99" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" ht="15" customHeight="1">
+      <c r="B100" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="9">
+        <v>715</v>
+      </c>
+      <c r="H100" s="10">
+        <v>0.0009027450142</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J100" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" ht="15" customHeight="1">
+      <c r="B101" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="F99" s="14">
-        <v>200000</v>
-      </c>
-      <c r="G99" s="15">
-        <v>198.08</v>
-      </c>
-      <c r="H99" s="16">
-        <v>0.0002664180996</v>
-      </c>
-      <c r="I99" s="15">
-        <v>6.43</v>
-      </c>
-      <c r="J99" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="100" spans="2:10" ht="15" customHeight="1">
-      <c r="B100" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J100" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="101" spans="2:10" ht="15" customHeight="1">
-      <c r="B101" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G101" s="9">
-        <v>4367.65</v>
-      </c>
-      <c r="H101" s="10">
-        <v>0.0058745002677</v>
-      </c>
-      <c r="I101" s="9" t="s">
+      <c r="C101" s="13"/>
+      <c r="D101" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="13"/>
+      <c r="G101" s="15">
+        <v>715</v>
+      </c>
+      <c r="H101" s="16">
+        <v>0.0009027450142</v>
+      </c>
+      <c r="I101" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J101" s="11" t="s">
@@ -4012,27 +3912,6 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
       <c r="B102" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="C102" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="D102" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="F102" s="14">
-        <v>1179999</v>
-      </c>
-      <c r="G102" s="15">
-        <v>4367.65</v>
-      </c>
-      <c r="H102" s="16">
-        <v>0.0058745002677</v>
-      </c>
-      <c r="I102" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J102" s="11" t="s">
@@ -4040,130 +3919,151 @@
       </c>
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
-      <c r="B103" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J103" s="11" t="s">
+      <c r="B103" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="C103" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="18">
+        <v>-2128.015760630369</v>
+      </c>
+      <c r="H103" s="19">
+        <v>-0.0026867910743239793</v>
+      </c>
+      <c r="I103" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J103" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
-      <c r="B104" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G104" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H104" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="I104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J104" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="105" spans="2:10" ht="15" customHeight="1">
-      <c r="B105" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J105" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="106" spans="2:10" ht="15" customHeight="1">
-      <c r="B106" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F106" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G106" s="9">
-        <v>39089.04</v>
-      </c>
-      <c r="H106" s="10">
-        <v>0.0525748574052</v>
-      </c>
-      <c r="I106" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J106" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="107" spans="2:10" ht="15" customHeight="1">
-      <c r="B107" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J107" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="108" spans="2:10" ht="15" customHeight="1">
+      <c r="B104" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="C104" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="18">
+        <v>792028.74423937</v>
+      </c>
+      <c r="H104" s="19">
+        <v>0.9999999999969755</v>
+      </c>
+      <c r="I104" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J104" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" ht="15" customHeight="1">
+      <c r="B106" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C106" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H106" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8" ht="15" customHeight="1">
+      <c r="B107" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D107" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E107" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F107" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G107" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H107" s="18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" ht="15" customHeight="1">
       <c r="B108" s="7" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D108" s="9" t="s">
+      <c r="D108" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E108" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G108" s="9">
-        <v>1005</v>
-      </c>
-      <c r="H108" s="10">
-        <v>0.0013517275351</v>
-      </c>
-      <c r="I108" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J108" s="11" t="s">
+      <c r="F108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H108" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
       <c r="B109" s="12" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C109" s="13"/>
       <c r="D109" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E109" s="13"/>
+      <c r="E109" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F109" s="14">
+        <v>532500</v>
+      </c>
       <c r="G109" s="15">
-        <v>1005</v>
+        <v>1234.49</v>
       </c>
       <c r="H109" s="16">
-        <v>0.0013517275351</v>
+        <v>0.0015586429267</v>
       </c>
       <c r="I109" s="15" t="s">
         <v>13</v>
@@ -4172,98 +4072,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="2:10" ht="15" customHeight="1">
-      <c r="B110" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J110" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="111" spans="2:10" ht="15" customHeight="1">
-      <c r="B111" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="C111" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D111" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E111" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F111" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G111" s="18">
-        <v>-1851.8006473700516</v>
-      </c>
-      <c r="H111" s="19">
-        <v>-0.002490676542028162</v>
-      </c>
-      <c r="I111" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J111" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="112" spans="2:10" ht="15" customHeight="1">
-      <c r="B112" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="C112" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D112" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E112" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F112" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G112" s="18">
-        <v>743493.02935263</v>
-      </c>
-      <c r="H112" s="19">
-        <v>0.9999999999964718</v>
-      </c>
-      <c r="I112" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J112" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="115" spans="2:9" ht="15" customHeight="1">
-      <c r="B115" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="C115" s="21"/>
-      <c r="D115" s="21"/>
-      <c r="E115" s="21"/>
-      <c r="F115" s="21"/>
-      <c r="G115" s="21"/>
-      <c r="H115" s="21"/>
-      <c r="I115" s="21"/>
-    </row>
-    <row r="116" spans="2:8" ht="15" customHeight="1">
-      <c r="B116" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="C116" s="21"/>
-      <c r="D116" s="21"/>
-      <c r="E116" s="21"/>
-      <c r="F116" s="21"/>
-      <c r="G116" s="21"/>
-      <c r="H116" s="21"/>
-    </row>
-    <row r="117" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B117" s="22" t="s">
-        <v>196</v>
+    <row r="113" spans="2:9" ht="15" customHeight="1">
+      <c r="B113" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C113" s="21"/>
+      <c r="D113" s="21"/>
+      <c r="E113" s="21"/>
+      <c r="F113" s="21"/>
+      <c r="G113" s="21"/>
+      <c r="H113" s="21"/>
+      <c r="I113" s="21"/>
+    </row>
+    <row r="117" spans="2:9" ht="15" customHeight="1">
+      <c r="B117" s="13" t="s">
+        <v>184</v>
       </c>
       <c r="C117" s="21"/>
       <c r="D117" s="21"/>
@@ -4271,10 +4094,11 @@
       <c r="F117" s="21"/>
       <c r="G117" s="21"/>
       <c r="H117" s="21"/>
-    </row>
-    <row r="118" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B118" s="22" t="s">
-        <v>197</v>
+      <c r="I117" s="21"/>
+    </row>
+    <row r="118" spans="2:8" ht="15" customHeight="1">
+      <c r="B118" s="13" t="s">
+        <v>185</v>
       </c>
       <c r="C118" s="21"/>
       <c r="D118" s="21"/>
@@ -4283,9 +4107,9 @@
       <c r="G118" s="21"/>
       <c r="H118" s="21"/>
     </row>
-    <row r="119" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B119" s="22" t="s">
-        <v>198</v>
+    <row r="119" spans="2:8" ht="15" customHeight="1">
+      <c r="B119" s="13" t="s">
+        <v>186</v>
       </c>
       <c r="C119" s="21"/>
       <c r="D119" s="21"/>
@@ -4294,31 +4118,61 @@
       <c r="G119" s="21"/>
       <c r="H119" s="21"/>
     </row>
-    <row r="122" ht="15">
-      <c r="B122" s="21" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="137" ht="15">
-      <c r="B137" s="21" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="138" ht="15">
-      <c r="B138" s="21" t="s">
-        <v>201</v>
+    <row r="120" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B120" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C120" s="21"/>
+      <c r="D120" s="21"/>
+      <c r="E120" s="21"/>
+      <c r="F120" s="21"/>
+      <c r="G120" s="21"/>
+      <c r="H120" s="21"/>
+    </row>
+    <row r="121" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B121" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="C121" s="21"/>
+      <c r="D121" s="21"/>
+      <c r="E121" s="21"/>
+      <c r="F121" s="21"/>
+      <c r="G121" s="21"/>
+      <c r="H121" s="21"/>
+    </row>
+    <row r="122" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B122" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="C122" s="21"/>
+      <c r="D122" s="21"/>
+      <c r="E122" s="21"/>
+      <c r="F122" s="21"/>
+      <c r="G122" s="21"/>
+      <c r="H122" s="21"/>
+    </row>
+    <row r="125" ht="15">
+      <c r="B125" s="21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="140" ht="15">
+      <c r="B140" s="21" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B117:H117"/>
+  <mergeCells count="10">
     <mergeCell ref="B118:H118"/>
     <mergeCell ref="B119:H119"/>
+    <mergeCell ref="B120:H120"/>
+    <mergeCell ref="B121:H121"/>
+    <mergeCell ref="B122:H122"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B115:I115"/>
-    <mergeCell ref="B116:H116"/>
+    <mergeCell ref="B113:I113"/>
+    <mergeCell ref="B117:I117"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
